--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35535-2026 artfynd.xlsx
+++ b/artfynd/A 35535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536525</v>
       </c>
       <c r="B2" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536530</v>
       </c>
       <c r="B3" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
